--- a/static/data/database/JSS1_Students.xlsx
+++ b/static/data/database/JSS1_Students.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JSS1 Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'JSS1 Students'!$A$1:$H$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'JSS1 Students'!$A$1:$H$51</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H71"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -473,28 +473,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>std001</t>
+          <t>std002</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Abdulhakeem</t>
+          <t>Ismail</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Maryam</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>Ahmad</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Dikko</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>08036544???</t>
+          <t>08081995313</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -511,32 +515,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>std002</t>
+          <t>std003</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ismail</t>
+          <t>Muhammed</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ahmad</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Dikko</t>
-        </is>
-      </c>
+          <t>Halima</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>08081995313</t>
+          <t>08033692673</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -553,7 +553,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>std003</t>
+          <t>std004</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -563,13 +563,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Halima</t>
+          <t>Aisha</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>08033692673</t>
+          <t>08187197550</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -591,23 +591,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>std004</t>
+          <t>std005</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Muhammed</t>
+          <t>Hamisu</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Aisha</t>
+          <t>Farhana</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>08187197550</t>
+          <t>09098999995</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -629,23 +629,23 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>std005</t>
+          <t>std006</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hamisu</t>
+          <t>Nuhu</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Farhana</t>
+          <t>Mariam</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>09098999995</t>
+          <t>07061663073</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -667,28 +667,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>std006</t>
+          <t>std008</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nuhu</t>
+          <t>Musa</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mariam</t>
+          <t>Yusuf</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>07061663073</t>
+          <t>08035863545</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -705,27 +705,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>std007</t>
+          <t>std009</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Adeyemi</t>
+          <t>Shakiru</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hafeez</t>
+          <t>A.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Harith</t>
+          <t>Mukaila</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>08027283163</t>
+          <t>08039445304</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -747,23 +747,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>std008</t>
+          <t>std010</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Musa</t>
+          <t>Muhammed</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Yusuf</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>A.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Abdulrahman</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>08035863545</t>
+          <t>08062705700</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -785,27 +789,23 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>std009</t>
+          <t>std011</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Shakiru</t>
+          <t>Muhammed</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>A.</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Mukaila</t>
-        </is>
-      </c>
+          <t>Lawal</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>08039445304</t>
+          <t>08109558724</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -827,27 +827,23 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>std010</t>
+          <t>std012</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Muhammed</t>
+          <t>Raji</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>A.</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Abdulrahman</t>
-        </is>
-      </c>
+          <t>Yasir</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>08062705700</t>
+          <t>08062445657</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -869,28 +865,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>std011</t>
+          <t>std014</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Muhammed</t>
+          <t>Umar</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lawal</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Sarki</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Khadijat</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>08109558724</t>
+          <t>08038345027</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -907,28 +907,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>std012</t>
+          <t>std016</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Raji</t>
+          <t>Mikal</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Yasir</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Bello</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Najaat</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>08062445657</t>
+          <t>08036937562</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -945,23 +949,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>std013</t>
+          <t>std017</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Abdulaziz</t>
+          <t>Sani</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kura</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Muhammad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Sani</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>08065353705</t>
+          <t>08036422777</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -983,32 +991,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>std014</t>
+          <t>std018</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Umar</t>
+          <t>Yusuf</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sarki</t>
+          <t>Alamin</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Khadijat</t>
+          <t>Afolabi</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>08038345027</t>
+          <t>08034000883</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1025,27 +1033,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>std015</t>
+          <t>std019</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Abbas</t>
+          <t>Sanusi</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bello</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Aisha</t>
-        </is>
-      </c>
+          <t>Suhaila</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0806517?03?</t>
+          <t>08069706494</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1067,32 +1071,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>std016</t>
+          <t>std020</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mikal</t>
+          <t>Sanusi</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bello</t>
+          <t>Suleiman</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Najaat</t>
+          <t>Sultan</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>08036937562</t>
+          <t>08068323637</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1109,27 +1113,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>std017</t>
+          <t>std021</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sani</t>
+          <t>Kebiru</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Muhammad</t>
+          <t>Yaseen</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Sani</t>
+          <t>Mohammed</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>08036422777</t>
+          <t>08068753880</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1151,7 +1155,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>std018</t>
+          <t>std022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1161,22 +1165,18 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Alamin</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Afolabi</t>
-        </is>
-      </c>
+          <t>Nazira</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>08034000883</t>
+          <t>00817801996</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1193,23 +1193,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>std019</t>
+          <t>std025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sanusi</t>
+          <t>Idiaro</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Suhaila</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Faheemah</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Faruk</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>08069706494</t>
+          <t>08033707400</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1219,7 +1223,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>JSS1A</t>
+          <t>JSS1B</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1231,37 +1235,33 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>std020</t>
+          <t>std026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sanusi</t>
+          <t>Galadima</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Suleiman</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Sultan</t>
-        </is>
-      </c>
+          <t>Zainab</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>08068323637</t>
+          <t>08039716953</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>JSS1A</t>
+          <t>JSS1B</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1273,37 +1273,33 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>std021</t>
+          <t>std028</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Kebiru</t>
+          <t>Muhammad</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Yaseen</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Mohammed</t>
-        </is>
-      </c>
+          <t>Hannifa</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>08068753880</t>
+          <t>07037935851</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>JSS1A</t>
+          <t>JSS1B</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1315,23 +1311,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>std022</t>
+          <t>std029</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>Saleh</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Aisha</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
           <t>Yusuf</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Nazira</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>00817801996</t>
+          <t>08032285755</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>JSS1A</t>
+          <t>JSS1B</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1353,27 +1353,23 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>std023</t>
+          <t>std031</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Adeyemi</t>
+          <t>Saeed</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Muklisah</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Adepeju</t>
-        </is>
-      </c>
+          <t>Maryam</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>08032190197</t>
+          <t>08128841017</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1395,27 +1391,23 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>std024</t>
+          <t>std032</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Abbakura</t>
+          <t>Kurama</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ali</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Sadiq</t>
-        </is>
-      </c>
+          <t>Aisha</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>08032109398</t>
+          <t>08033138074</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1437,27 +1429,23 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>std025</t>
+          <t>std033</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Idiaro</t>
+          <t>Yusuf</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Faheemah</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Faruk</t>
-        </is>
-      </c>
+          <t>Ummulqulsum</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>08033707400</t>
+          <t>08023039467</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1479,23 +1467,27 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>std026</t>
+          <t>std034</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Galadima</t>
+          <t>Ibrahim</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Zainab</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+          <t>Habiba</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Yasmin</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>08039716953</t>
+          <t>08032888858?</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1517,32 +1509,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>std027</t>
+          <t>std036</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Abbakura</t>
+          <t>Bashir</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ali</t>
+          <t>Usman</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Zaynab</t>
+          <t>Muhammad</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>08032109398</t>
+          <t>08033120726</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1559,28 +1551,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>std028</t>
+          <t>std038</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Muhammad</t>
+          <t>Kashim</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Hannifa</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
+          <t>Ali</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Marte</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>07037935851</t>
+          <t>08036975970</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1597,32 +1593,28 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>std029</t>
+          <t>std039</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Saleh</t>
+          <t>Muhammad</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Aisha</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Yusuf</t>
-        </is>
-      </c>
+          <t>Zanna</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>08032285755</t>
+          <t>08069638793</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1639,28 +1631,28 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>std030</t>
+          <t>std041</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Audu</t>
+          <t>Yahaya</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Fadilah</t>
+          <t>Bila?</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>08033738117</t>
+          <t>08064609629</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1677,28 +1669,28 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>std031</t>
+          <t>std042</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Saeed</t>
+          <t>Tijani</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Maryam</t>
+          <t>Aliyu</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>08128841017</t>
+          <t>08034625133</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1715,28 +1707,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>std032</t>
+          <t>std043</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Kurama</t>
+          <t>Sanusi</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Aisha</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
+          <t>Isa</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Muhammad</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>08033138074</t>
+          <t>08037760678</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1753,28 +1749,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>std033</t>
+          <t>std044</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Yusuf</t>
+          <t>Muhammed</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ummulqulsum</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
+          <t>Aliyu</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Oga</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>08023039467</t>
+          <t>08037310224</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1791,27 +1791,27 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>std034</t>
+          <t>std045</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Ibrahim</t>
+          <t>Ilyas</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Habiba</t>
+          <t>Zafeerah</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Yasmin</t>
+          <t>Oyiza</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>08032888858?</t>
+          <t>040169477296?</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1833,28 +1833,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>std035</t>
+          <t>std046</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Abubakar</t>
+          <t>Zainat</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ibrahim</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
+          <t>Abdullahi</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Muhammad</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>08035839220</t>
+          <t>08032050105</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1871,37 +1875,33 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>std036</t>
+          <t>std051</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Bashir</t>
+          <t>Azeezatun</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Usman</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Muhammad</t>
-        </is>
-      </c>
+          <t>Azizat</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>08033120726</t>
+          <t>07063514237</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>JSS1B</t>
+          <t>JSS1C</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1913,37 +1913,33 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>std037</t>
+          <t>std056</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Abdulhakeem</t>
+          <t>Badirah</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Muhammad</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Al-amin</t>
-        </is>
-      </c>
+          <t>Kolawole</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>08062518827</t>
+          <t>07057948726</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>JSS1B</t>
+          <t>JSS1C</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1955,27 +1951,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>std038</t>
+          <t>std057</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Kashim</t>
+          <t>Nasir</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ali</t>
+          <t>Mustapha</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Marte</t>
+          <t>Sale</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>08036975970</t>
+          <t>08169655379</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1985,7 +1981,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>JSS1B</t>
+          <t>JSS1C</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1997,33 +1993,33 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>std039</t>
+          <t>std058</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Muhammad</t>
+          <t>Maryam</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Zanna</t>
+          <t>Nasiru</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>08069638793</t>
+          <t>07064493005</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>JSS1B</t>
+          <t>JSS1C</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2035,33 +2031,33 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>std040</t>
+          <t>std059</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Abbas</t>
+          <t>Mustapha</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Muaz</t>
+          <t>Karima</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>08036964091</t>
+          <t>08033226007</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>JSS1B</t>
+          <t>JSS1C</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2073,23 +2069,23 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>std041</t>
+          <t>std060</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Yahaya</t>
+          <t>Sani</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bila?</t>
+          <t>Uruwatu</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>08064609629</t>
+          <t>08032724699</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2099,7 +2095,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>JSS1B</t>
+          <t>JSS1C</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2111,23 +2107,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>std042</t>
+          <t>std061</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Tijani</t>
+          <t>Imran</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Aliyu</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
+          <t>Muhammad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Shamsudeen</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>08034625133</t>
+          <t>08063708311</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>JSS1B</t>
+          <t>JSS1C</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2149,37 +2149,37 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>std043</t>
+          <t>std062</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Sanusi</t>
+          <t>Heebatulah</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Isa</t>
+          <t>Oluyemoh</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Muhammad</t>
+          <t>Jenrola</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>08037760678</t>
+          <t>08033868455</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>JSS1B</t>
+          <t>JSS1C</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2191,37 +2191,37 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>std044</t>
+          <t>std063</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Muhammed</t>
+          <t>Zainab</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Aliyu</t>
+          <t>Abdullahi</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Oga</t>
+          <t>Muhammad</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>08037310224</t>
+          <t>08035861015</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>JSS1B</t>
+          <t>JSS1C</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2233,37 +2233,37 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>std045</t>
+          <t>std065</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ilyas</t>
+          <t>Tijani</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Zafeerah</t>
+          <t>Faruq</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Oyiza</t>
+          <t>Jubril</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>040169477296?</t>
+          <t>08069057075</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>JSS1B</t>
+          <t>JSS1C</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2275,27 +2275,23 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>std046</t>
+          <t>std066</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Zainat</t>
+          <t>Hauwa</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Abdullahi</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Muhammad</t>
-        </is>
-      </c>
+          <t>Musa</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>08032050105</t>
+          <t>08033267564</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2305,7 +2301,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>JSS1B</t>
+          <t>JSS1C</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2317,28 +2313,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>std047</t>
+          <t>std067</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Abdulrahman</t>
+          <t>Zainab</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Auwal</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
+          <t>Abubakar</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Astar</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>08033973137</t>
+          <t>08030569524</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2355,28 +2355,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>std048</t>
+          <t>std068</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Abdulrahim</t>
+          <t>Ilyas</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Saad</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
+          <t>Zafeerah</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Oyiza</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>08032865130</t>
+          <t>09016247296</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2393,23 +2397,27 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>std049</t>
+          <t>std069</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Abdullahi</t>
+          <t>Muhammad</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Abdulrahman</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
+          <t>Salim</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Bashir</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>08062732619</t>
+          <t>09019126757</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2431,32 +2439,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>std050</t>
+          <t>std070</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Abdulmalik</t>
+          <t>Mariam</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Muhammad</t>
+          <t>Nuhu</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Ubandoma</t>
+          <t>Omakwoka</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>07068718854</t>
+          <t>07061663073</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2470,816 +2478,8 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>std051</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Azeezatun</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Azizat</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>07063514237</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>JSS1C</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>JSS1</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>std052</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Anointed</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Peter</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Onoja</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>08067028585</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>JSS1C</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>JSS1</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>std053</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Akinloye</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Goodness</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>08058010495</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>JSS1C</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>JSS1</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>std054</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Amar</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Nimlan</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>09060778131</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>JSS1C</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>JSS1</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>std055</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Abba</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Mamman</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Ummahani</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>08031357581</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>JSS1C</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>JSS1</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>std056</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Badirah</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Kolawole</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>07057948726</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>JSS1C</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>JSS1</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>std057</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Nasir</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Mustapha</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Sale</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>08169655379</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>JSS1C</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>JSS1</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>std058</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Maryam</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Nasiru</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>07064493005</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>JSS1C</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>JSS1</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>std059</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Mustapha</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Karima</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>08033226007</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>JSS1C</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>JSS1</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>std060</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Sani</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Uruwatu</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>08032724699</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>JSS1C</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>JSS1</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>std061</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Imran</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Muhammad</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Shamsudeen</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>08063708311</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>JSS1C</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>JSS1</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>std062</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Heebatulah</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Oluyemoh</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Jenrola</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>08033868455</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>JSS1C</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>JSS1</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>std063</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Zainab</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Abdullahi</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Muhammad</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>08035861015</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>JSS1C</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>JSS1</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>std064</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Abdullahi</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Adamu</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Sambo</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>07065914224</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>JSS1C</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>JSS1</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>std065</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Tijani</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Faruq</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Jubril</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>08069057075</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>JSS1C</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>JSS1</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>std066</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Hauwa</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Musa</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>08033267564</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>JSS1C</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>JSS1</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>std067</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Zainab</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Abubakar</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Astar</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>08030569524</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>JSS1C</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>JSS1</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>std068</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Ilyas</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Zafeerah</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Oyiza</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>09016247296</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>JSS1C</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>JSS1</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>std069</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Muhammad</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Salim</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Bashir</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>09019126757</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>JSS1C</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>JSS1</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>std070</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Mariam</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Nuhu</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Omakwoka</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>07061663073</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>JSS1C</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>JSS1</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H71"/>
+  <autoFilter ref="A1:H51"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/static/data/database/JSS1_Students.xlsx
+++ b/static/data/database/JSS1_Students.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JSS1 Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'JSS1 Students'!$A$1:$H$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'JSS1 Students'!$A$1:$H$71</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -473,32 +473,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>std002</t>
+          <t>std001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ismail</t>
+          <t>Abdulhakeem</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ahmad</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Dikko</t>
-        </is>
-      </c>
+          <t>Maryam</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>08081995313</t>
+          <t>08036544???</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -515,28 +511,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>std003</t>
+          <t>std002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Muhammed</t>
+          <t>Ismail</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Halima</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>Ahmad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Dikko</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>08033692673</t>
+          <t>08081995313</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -553,7 +553,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>std004</t>
+          <t>std003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -563,13 +563,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Aisha</t>
+          <t>Halima</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>08187197550</t>
+          <t>08033692673</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -591,23 +591,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>std005</t>
+          <t>std004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hamisu</t>
+          <t>Muhammed</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Farhana</t>
+          <t>Aisha</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>09098999995</t>
+          <t>08187197550</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -629,23 +629,23 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>std006</t>
+          <t>std005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nuhu</t>
+          <t>Hamisu</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mariam</t>
+          <t>Farhana</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>07061663073</t>
+          <t>09098999995</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -667,28 +667,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>std008</t>
+          <t>std006</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Musa</t>
+          <t>Nuhu</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yusuf</t>
+          <t>Mariam</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>08035863545</t>
+          <t>07061663073</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -705,27 +705,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>std009</t>
+          <t>std007</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Shakiru</t>
+          <t>Adeyemi</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>A.</t>
+          <t>Hafeez</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Mukaila</t>
+          <t>Harith</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>08039445304</t>
+          <t>08027283163</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -747,27 +747,23 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>std010</t>
+          <t>std008</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Muhammed</t>
+          <t>Musa</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>A.</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Abdulrahman</t>
-        </is>
-      </c>
+          <t>Yusuf</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>08062705700</t>
+          <t>08035863545</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -789,23 +785,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>std011</t>
+          <t>std009</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Muhammed</t>
+          <t>Shakiru</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lawal</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>A.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Mukaila</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>08109558724</t>
+          <t>08039445304</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -827,23 +827,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>std012</t>
+          <t>std010</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Raji</t>
+          <t>Muhammed</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Yasir</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>A.</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Abdulrahman</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>08062445657</t>
+          <t>08062705700</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -865,32 +869,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>std014</t>
+          <t>std011</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Umar</t>
+          <t>Muhammed</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sarki</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Khadijat</t>
-        </is>
-      </c>
+          <t>Lawal</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>08038345027</t>
+          <t>08109558724</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -907,32 +907,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>std016</t>
+          <t>std012</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mikal</t>
+          <t>Raji</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bello</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Najaat</t>
-        </is>
-      </c>
+          <t>Yasir</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>08036937562</t>
+          <t>08062445657</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -949,27 +945,23 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>std017</t>
+          <t>std013</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sani</t>
+          <t>Abdulaziz</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Muhammad</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Sani</t>
-        </is>
-      </c>
+          <t>Kura</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>08036422777</t>
+          <t>08065353705</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -991,32 +983,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>std018</t>
+          <t>std014</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Yusuf</t>
+          <t>Umar</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Alamin</t>
+          <t>Sarki</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Afolabi</t>
+          <t>Khadijat</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>08034000883</t>
+          <t>08038345027</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1033,23 +1025,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>std019</t>
+          <t>std015</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sanusi</t>
+          <t>Abbas</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Suhaila</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Bello</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Aisha</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>08069706494</t>
+          <t>0806517?03?</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1071,32 +1067,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>std020</t>
+          <t>std016</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sanusi</t>
+          <t>Mikal</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Suleiman</t>
+          <t>Bello</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Sultan</t>
+          <t>Najaat</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>08068323637</t>
+          <t>08036937562</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1113,27 +1109,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>std021</t>
+          <t>std017</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Kebiru</t>
+          <t>Sani</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yaseen</t>
+          <t>Muhammad</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Mohammed</t>
+          <t>Sani</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>08068753880</t>
+          <t>08036422777</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1155,7 +1151,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>std022</t>
+          <t>std018</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1165,18 +1161,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Nazira</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Alamin</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Afolabi</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>00817801996</t>
+          <t>08034000883</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1193,27 +1193,23 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>std025</t>
+          <t>std019</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Idiaro</t>
+          <t>Sanusi</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Faheemah</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Faruk</t>
-        </is>
-      </c>
+          <t>Suhaila</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>08033707400</t>
+          <t>08069706494</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1223,7 +1219,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>JSS1B</t>
+          <t>JSS1A</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1235,33 +1231,37 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>std026</t>
+          <t>std020</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Galadima</t>
+          <t>Sanusi</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Zainab</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Suleiman</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Sultan</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>08039716953</t>
+          <t>08068323637</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>JSS1B</t>
+          <t>JSS1A</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1273,33 +1273,37 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>std028</t>
+          <t>std021</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Muhammad</t>
+          <t>Kebiru</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Hannifa</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>Yaseen</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Mohammed</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>07037935851</t>
+          <t>08068753880</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>JSS1B</t>
+          <t>JSS1A</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1311,27 +1315,23 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>std029</t>
+          <t>std022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Saleh</t>
+          <t>Yusuf</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Aisha</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Yusuf</t>
-        </is>
-      </c>
+          <t>Nazira</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>08032285755</t>
+          <t>00817801996</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>JSS1B</t>
+          <t>JSS1A</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1353,23 +1353,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>std031</t>
+          <t>std023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Saeed</t>
+          <t>Adeyemi</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Maryam</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>Muklisah</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Adepeju</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>08128841017</t>
+          <t>08032190197</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1391,23 +1395,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>std032</t>
+          <t>std024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Kurama</t>
+          <t>Abbakura</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Aisha</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>Ali</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Sadiq</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>08033138074</t>
+          <t>08032109398</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1429,23 +1437,27 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>std033</t>
+          <t>std025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Yusuf</t>
+          <t>Idiaro</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ummulqulsum</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>Faheemah</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Faruk</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>08023039467</t>
+          <t>08033707400</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1467,27 +1479,23 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>std034</t>
+          <t>std026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ibrahim</t>
+          <t>Galadima</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Habiba</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Yasmin</t>
-        </is>
-      </c>
+          <t>Zainab</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>08032888858?</t>
+          <t>08039716953</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1509,32 +1517,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>std036</t>
+          <t>std027</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Bashir</t>
+          <t>Abbakura</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Usman</t>
+          <t>Ali</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Muhammad</t>
+          <t>Zaynab</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>08033120726</t>
+          <t>08032109398</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1551,32 +1559,28 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>std038</t>
+          <t>std028</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Kashim</t>
+          <t>Muhammad</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ali</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Marte</t>
-        </is>
-      </c>
+          <t>Hannifa</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>08036975970</t>
+          <t>07037935851</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1593,28 +1597,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>std039</t>
+          <t>std029</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Muhammad</t>
+          <t>Saleh</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Zanna</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
+          <t>Aisha</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Yusuf</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>08069638793</t>
+          <t>08032285755</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1631,28 +1639,28 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>std041</t>
+          <t>std030</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Yahaya</t>
+          <t>Audu</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bila?</t>
+          <t>Fadilah</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>08064609629</t>
+          <t>08033738117</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1669,28 +1677,28 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>std042</t>
+          <t>std031</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Tijani</t>
+          <t>Saeed</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Aliyu</t>
+          <t>Maryam</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>08034625133</t>
+          <t>08128841017</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1707,32 +1715,28 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>std043</t>
+          <t>std032</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Sanusi</t>
+          <t>Kurama</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Isa</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Muhammad</t>
-        </is>
-      </c>
+          <t>Aisha</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>08037760678</t>
+          <t>08033138074</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1749,32 +1753,28 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>std044</t>
+          <t>std033</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Muhammed</t>
+          <t>Yusuf</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Aliyu</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Oga</t>
-        </is>
-      </c>
+          <t>Ummulqulsum</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>08037310224</t>
+          <t>08023039467</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1791,27 +1791,27 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>std045</t>
+          <t>std034</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Ilyas</t>
+          <t>Ibrahim</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Zafeerah</t>
+          <t>Habiba</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Oyiza</t>
+          <t>Yasmin</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>040169477296?</t>
+          <t>08032888858?</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1833,32 +1833,28 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>std046</t>
+          <t>std035</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Zainat</t>
+          <t>Abubakar</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Abdullahi</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Muhammad</t>
-        </is>
-      </c>
+          <t>Ibrahim</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>08032050105</t>
+          <t>08035839220</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1875,33 +1871,37 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>std051</t>
+          <t>std036</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Azeezatun</t>
+          <t>Bashir</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Azizat</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
+          <t>Usman</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Muhammad</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>07063514237</t>
+          <t>08033120726</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>JSS1C</t>
+          <t>JSS1B</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1913,33 +1913,37 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>std056</t>
+          <t>std037</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Badirah</t>
+          <t>Abdulhakeem</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Kolawole</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
+          <t>Muhammad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Al-amin</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>07057948726</t>
+          <t>08062518827</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>JSS1C</t>
+          <t>JSS1B</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1951,27 +1955,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>std057</t>
+          <t>std038</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Nasir</t>
+          <t>Kashim</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Mustapha</t>
+          <t>Ali</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Sale</t>
+          <t>Marte</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>08169655379</t>
+          <t>08036975970</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1981,7 +1985,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>JSS1C</t>
+          <t>JSS1B</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1993,33 +1997,33 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>std058</t>
+          <t>std039</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Maryam</t>
+          <t>Muhammad</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Nasiru</t>
+          <t>Zanna</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>07064493005</t>
+          <t>08069638793</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>JSS1C</t>
+          <t>JSS1B</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2031,33 +2035,33 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>std059</t>
+          <t>std040</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Mustapha</t>
+          <t>Abbas</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Karima</t>
+          <t>Muaz</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>08033226007</t>
+          <t>08036964091</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>JSS1C</t>
+          <t>JSS1B</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2069,23 +2073,23 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>std060</t>
+          <t>std041</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Sani</t>
+          <t>Yahaya</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Uruwatu</t>
+          <t>Bila?</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>08032724699</t>
+          <t>08064609629</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2095,7 +2099,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>JSS1C</t>
+          <t>JSS1B</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2107,27 +2111,23 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>std061</t>
+          <t>std042</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Imran</t>
+          <t>Tijani</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Muhammad</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Shamsudeen</t>
-        </is>
-      </c>
+          <t>Aliyu</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>08063708311</t>
+          <t>08034625133</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>JSS1C</t>
+          <t>JSS1B</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2149,37 +2149,37 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>std062</t>
+          <t>std043</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Heebatulah</t>
+          <t>Sanusi</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Oluyemoh</t>
+          <t>Isa</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Jenrola</t>
+          <t>Muhammad</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>08033868455</t>
+          <t>08037760678</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>JSS1C</t>
+          <t>JSS1B</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2191,37 +2191,37 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>std063</t>
+          <t>std044</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Zainab</t>
+          <t>Muhammed</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Abdullahi</t>
+          <t>Aliyu</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Muhammad</t>
+          <t>Oga</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>08035861015</t>
+          <t>08037310224</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>JSS1C</t>
+          <t>JSS1B</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2233,37 +2233,37 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>std065</t>
+          <t>std045</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Tijani</t>
+          <t>Ilyas</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Faruq</t>
+          <t>Zafeerah</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Jubril</t>
+          <t>Oyiza</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>08069057075</t>
+          <t>040169477296?</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>JSS1C</t>
+          <t>JSS1B</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2275,23 +2275,27 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>std066</t>
+          <t>std046</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Hauwa</t>
+          <t>Zainat</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Musa</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
+          <t>Abdullahi</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Muhammad</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>08033267564</t>
+          <t>08032050105</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2301,7 +2305,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>JSS1C</t>
+          <t>JSS1B</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2313,32 +2317,28 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>std067</t>
+          <t>std047</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Zainab</t>
+          <t>Abdulrahman</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Abubakar</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Astar</t>
-        </is>
-      </c>
+          <t>Auwal</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>08030569524</t>
+          <t>08033973137</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2355,32 +2355,28 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>std068</t>
+          <t>std048</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ilyas</t>
+          <t>Abdulrahim</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Zafeerah</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Oyiza</t>
-        </is>
-      </c>
+          <t>Saad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>09016247296</t>
+          <t>08032865130</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2397,27 +2393,23 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>std069</t>
+          <t>std049</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Muhammad</t>
+          <t>Abdullahi</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Salim</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Bashir</t>
-        </is>
-      </c>
+          <t>Abdulrahman</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>09019126757</t>
+          <t>08062732619</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2439,47 +2431,855 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>std050</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Abdulmalik</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Muhammad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Ubandoma</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>07068718854</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>JSS1C</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>JSS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>std051</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Azeezatun</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Azizat</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>07063514237</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>JSS1C</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>JSS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>std052</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Anointed</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Onoja</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>08067028585</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>JSS1C</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>JSS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>std053</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Akinloye</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Goodness</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>08058010495</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>JSS1C</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>JSS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>std054</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Amar</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Nimlan</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>09060778131</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>JSS1C</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>JSS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>std055</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Abba</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Mamman</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Ummahani</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>08031357581</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>JSS1C</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>JSS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>std056</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Badirah</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Kolawole</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>07057948726</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>JSS1C</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>JSS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>std057</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Nasir</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Mustapha</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>08169655379</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>JSS1C</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>JSS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>std058</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Maryam</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Nasiru</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>07064493005</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>JSS1C</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>JSS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>std059</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Mustapha</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Karima</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>08033226007</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>JSS1C</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>JSS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>std060</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Sani</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Uruwatu</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>08032724699</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>JSS1C</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>JSS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>std061</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Imran</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Muhammad</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Shamsudeen</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>08063708311</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>JSS1C</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>JSS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>std062</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Heebatulah</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Oluyemoh</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Jenrola</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>08033868455</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>JSS1C</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>JSS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>std063</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Zainab</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Abdullahi</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Muhammad</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>08035861015</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>JSS1C</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>JSS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>std064</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Abdullahi</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Adamu</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Sambo</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>07065914224</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>JSS1C</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>JSS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>std065</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Tijani</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Faruq</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Jubril</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>08069057075</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>JSS1C</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>JSS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>std066</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Hauwa</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Musa</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>08033267564</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>JSS1C</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>JSS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>std067</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Zainab</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Abubakar</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Astar</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>08030569524</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>JSS1C</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>JSS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>std068</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Ilyas</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Zafeerah</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Oyiza</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>09016247296</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>JSS1C</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>JSS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>std069</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Muhammad</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Salim</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Bashir</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>09019126757</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>JSS1C</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>JSS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
           <t>std070</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>Mariam</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>Nuhu</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>Omakwoka</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>07061663073</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
         <is>
           <t>JSS1C</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="H71" t="inlineStr">
         <is>
           <t>JSS1</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H51"/>
+  <autoFilter ref="A1:H71"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>